--- a/data/trans_orig/P05A06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P05A06-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2012</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2012 (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142424</t>
+          <t>142877</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178526</t>
+          <t>177786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,47 +747,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>49,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>137475</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>120530</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>155611</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>49,5%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>137475</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>119730</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>156646</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>49,5%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>274157</t>
+          <t>272283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321805</t>
+          <t>321935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81471</t>
+          <t>84204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116432</t>
+          <t>116628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126805</t>
+          <t>125910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183678</t>
+          <t>184933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231987</t>
+          <t>232662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41001</t>
+          <t>40368</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19803</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>43321</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>46575</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75340</t>
+          <t>76101</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316460</t>
+          <t>316546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358850</t>
+          <t>360791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327202</t>
+          <t>325350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371203</t>
+          <t>369755</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>653638</t>
+          <t>656628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>720762</t>
+          <t>718576</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132313</t>
+          <t>130863</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173362</t>
+          <t>174225</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131738</t>
+          <t>131057</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>173281</t>
+          <t>173954</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>271874</t>
+          <t>270798</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335010</t>
+          <t>331404</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24519</t>
+          <t>23238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>13248</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>24339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50193</t>
+          <t>49951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>261919</t>
+          <t>261363</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>286745</t>
+          <t>286184</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>281920</t>
+          <t>281994</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>307364</t>
+          <t>307551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>550791</t>
+          <t>550854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>588029</t>
+          <t>587305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34995</t>
+          <t>35429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59116</t>
+          <t>59405</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31202</t>
+          <t>30476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55475</t>
+          <t>55640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71660</t>
+          <t>72145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107826</t>
+          <t>107479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229487</t>
+          <t>227139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>266896</t>
+          <t>266208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234909</t>
+          <t>237354</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>271833</t>
+          <t>272946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>473937</t>
+          <t>476934</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>527923</t>
+          <t>532098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,42%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82537</t>
+          <t>82922</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117267</t>
+          <t>118920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98393</t>
+          <t>96727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134029</t>
+          <t>131585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189707</t>
+          <t>187218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>238654</t>
+          <t>241118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14777</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34813</t>
+          <t>35750</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24890</t>
+          <t>24259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>28319</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50672</t>
+          <t>52536</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>114477</t>
+          <t>114431</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143464</t>
+          <t>142930</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106790</t>
+          <t>107171</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>136486</t>
+          <t>138372</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>230744</t>
+          <t>231579</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>272463</t>
+          <t>273523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47964</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74727</t>
+          <t>75283</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69306</t>
+          <t>68647</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98313</t>
+          <t>98203</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>124385</t>
+          <t>124810</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>163023</t>
+          <t>164827</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34262</t>
+          <t>32689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22355</t>
+          <t>22753</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25731</t>
+          <t>25526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49577</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>206248</t>
+          <t>205816</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>233553</t>
+          <t>233036</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>198397</t>
+          <t>198009</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>226670</t>
+          <t>226893</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>413778</t>
+          <t>415917</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>451470</t>
+          <t>453166</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34506</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61430</t>
+          <t>60939</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48396</t>
+          <t>48915</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76902</t>
+          <t>77369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91622</t>
+          <t>91967</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>128690</t>
+          <t>128435</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>472804</t>
+          <t>472028</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>517196</t>
+          <t>518033</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>516886</t>
+          <t>515182</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>561859</t>
+          <t>561394</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>998796</t>
+          <t>1002771</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1068061</t>
+          <t>1066788</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>126942</t>
+          <t>125785</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>171835</t>
+          <t>170661</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>115136</t>
+          <t>116325</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>159690</t>
+          <t>161149</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>254619</t>
+          <t>253263</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>319937</t>
+          <t>316017</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23620</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23892</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40756</t>
+          <t>42150</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>530847</t>
+          <t>530646</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>583115</t>
+          <t>581492</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>567486</t>
+          <t>571267</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>623929</t>
+          <t>624442</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1116867</t>
+          <t>1115754</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1192647</t>
+          <t>1189938</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,33%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>171299</t>
+          <t>173080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>221414</t>
+          <t>223001</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>183491</t>
+          <t>182027</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>239263</t>
+          <t>235554</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>368570</t>
+          <t>369628</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>441829</t>
+          <t>443101</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>37295</t>
+          <t>36474</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26996</t>
+          <t>27630</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>29551</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55765</t>
+          <t>55718</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2370677</t>
+          <t>2373160</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2484371</t>
+          <t>2480058</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2448334</t>
+          <t>2451318</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2564878</t>
+          <t>2558730</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4860721</t>
+          <t>4862065</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5018440</t>
+          <t>5015343</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>794985</t>
+          <t>796370</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>901057</t>
+          <t>895318</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>855530</t>
+          <t>863626</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>961751</t>
+          <t>967037</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1680810</t>
+          <t>1683984</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1827751</t>
+          <t>1830193</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>111618</t>
+          <t>113910</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>158155</t>
+          <t>159441</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>99266</t>
+          <t>97803</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>143646</t>
+          <t>141059</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>225439</t>
+          <t>221422</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>285568</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2016</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>147125</t>
+          <t>145807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181825</t>
+          <t>182097</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140180</t>
+          <t>139373</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172706</t>
+          <t>173631</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>295909</t>
+          <t>297128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>345499</t>
+          <t>346397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,75%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86310</t>
+          <t>86979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119722</t>
+          <t>121675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88919</t>
+          <t>88547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121252</t>
+          <t>121992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185311</t>
+          <t>184981</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>235241</t>
+          <t>233373</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29238</t>
+          <t>29667</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31062</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27985</t>
+          <t>27385</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54191</t>
+          <t>54130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325345</t>
+          <t>326061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368973</t>
+          <t>367701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353520</t>
+          <t>353851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>396669</t>
+          <t>396074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691738</t>
+          <t>692881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>751363</t>
+          <t>751420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113691</t>
+          <t>114242</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>154320</t>
+          <t>153125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102988</t>
+          <t>105283</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143163</t>
+          <t>143404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>229319</t>
+          <t>228911</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>285299</t>
+          <t>285753</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32439</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>31564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>30947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57869</t>
+          <t>57954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>239898</t>
+          <t>240311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>267402</t>
+          <t>267157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>254690</t>
+          <t>255334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>284159</t>
+          <t>284387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>505178</t>
+          <t>505543</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>543744</t>
+          <t>544818</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45677</t>
+          <t>46183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72833</t>
+          <t>72230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48636</t>
+          <t>47399</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77262</t>
+          <t>76179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100445</t>
+          <t>100005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137800</t>
+          <t>138850</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>17655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>251360</t>
+          <t>252551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>287336</t>
+          <t>286188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>265729</t>
+          <t>266546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>302520</t>
+          <t>300390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>529400</t>
+          <t>530901</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>578168</t>
+          <t>578268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58672</t>
+          <t>59384</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90786</t>
+          <t>89769</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>58194</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87478</t>
+          <t>87601</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126026</t>
+          <t>126002</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>168108</t>
+          <t>168943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>16191</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>34179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,49 +6681,49 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>24320</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>35856</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>9,42%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>24320</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>15896</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>35305</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>45</t>
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35684</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63328</t>
+          <t>63099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>173481</t>
+          <t>173190</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191961</t>
+          <t>192442</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>176094</t>
+          <t>176364</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>196971</t>
+          <t>196616</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>358099</t>
+          <t>356844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384903</t>
+          <t>384040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14194</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31704</t>
+          <t>32549</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30006</t>
+          <t>31624</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>53760</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25202</t>
+          <t>25412</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>225794</t>
+          <t>224675</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245758</t>
+          <t>245135</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>239566</t>
+          <t>238718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>258062</t>
+          <t>257725</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>471967</t>
+          <t>470417</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>498888</t>
+          <t>498254</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>33588</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32514</t>
+          <t>33362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33603</t>
+          <t>33435</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59374</t>
+          <t>59207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>963</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>403147</t>
+          <t>401242</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>455797</t>
+          <t>450728</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>409800</t>
+          <t>409929</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>462818</t>
+          <t>461162</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>827945</t>
+          <t>828543</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>902420</t>
+          <t>897139</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>176303</t>
+          <t>177668</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>225531</t>
+          <t>226182</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>198971</t>
+          <t>200618</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>250883</t>
+          <t>251558</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>388891</t>
+          <t>392194</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>460513</t>
+          <t>459555</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35879</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34210</t>
+          <t>34065</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61291</t>
+          <t>61313</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>675744</t>
+          <t>674304</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>709106</t>
+          <t>708619</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>692221</t>
+          <t>691167</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>731539</t>
+          <t>732116</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1379207</t>
+          <t>1377243</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1431743</t>
+          <t>1431797</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>54045</t>
+          <t>54583</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>85078</t>
+          <t>85782</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>72346</t>
+          <t>73853</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>111130</t>
+          <t>113288</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>137642</t>
+          <t>136368</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>186299</t>
+          <t>188341</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23504</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,47 +8505,47 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>15504</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>8983</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>25681</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>15504</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>9253</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>25748</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20950</t>
+          <t>21149</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>43145</t>
+          <t>41990</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2526537</t>
+          <t>2530597</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2624790</t>
+          <t>2631855</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2616736</t>
+          <t>2625532</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2725308</t>
+          <t>2731399</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5180940</t>
+          <t>5180660</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5324212</t>
+          <t>5323665</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>636959</t>
+          <t>634101</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>731125</t>
+          <t>727126</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>671500</t>
+          <t>667810</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>772633</t>
+          <t>768259</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1333673</t>
+          <t>1329451</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1465255</t>
+          <t>1472085</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>97728</t>
+          <t>98658</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>142097</t>
+          <t>141005</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>97066</t>
+          <t>98995</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>141938</t>
+          <t>141886</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>206895</t>
+          <t>207919</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>269308</t>
+          <t>270301</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2023</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>290036</t>
+          <t>291105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>303804</t>
+          <t>304236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>254857</t>
+          <t>253358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279587</t>
+          <t>279389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>551642</t>
+          <t>552065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>580632</t>
+          <t>580766</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20125</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34906</t>
+          <t>36080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19085</t>
+          <t>18893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48137</t>
+          <t>47718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -9638,97 +9638,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1799</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>919</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370266</t>
+          <t>368414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420374</t>
+          <t>420591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>376845</t>
+          <t>374825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>411890</t>
+          <t>411818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>757024</t>
+          <t>758763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>820402</t>
+          <t>818694</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,37%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71968</t>
+          <t>70394</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>115999</t>
+          <t>115895</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88429</t>
+          <t>87899</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>122722</t>
+          <t>124412</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>171534</t>
+          <t>168810</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>228715</t>
+          <t>227132</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51704</t>
+          <t>51014</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20832</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66216</t>
+          <t>64709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>254850</t>
+          <t>255338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>279942</t>
+          <t>281232</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>289177</t>
+          <t>287408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>311066</t>
+          <t>311032</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>552602</t>
+          <t>549645</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>586399</t>
+          <t>585656</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,18%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37985</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,49 +10452,49 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>31796</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22781</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>42092</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>12,06%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>31796</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>23704</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>43729</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>77</t>
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46508</t>
+          <t>46862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73950</t>
+          <t>73983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30521</t>
+          <t>30306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>25663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25550</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48716</t>
+          <t>50460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>243857</t>
+          <t>243342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>274315</t>
+          <t>274050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>396004</t>
+          <t>396565</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>438180</t>
+          <t>439326</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>649697</t>
+          <t>651596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>704368</t>
+          <t>706987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30819</t>
+          <t>30927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58023</t>
+          <t>58047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27622</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63533</t>
+          <t>62774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66611</t>
+          <t>63205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113049</t>
+          <t>111610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>23589</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34726</t>
+          <t>36096</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154690</t>
+          <t>153880</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169558</t>
+          <t>169100</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237785</t>
+          <t>237919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251374</t>
+          <t>251369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398083</t>
+          <t>397847</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>418212</t>
+          <t>418323</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>24742</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19094</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>39336</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>919</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,62 +11497,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>822</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>227114</t>
+          <t>225457</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245747</t>
+          <t>245580</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>219666</t>
+          <t>220476</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>235566</t>
+          <t>236364</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>452402</t>
+          <t>453148</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>477209</t>
+          <t>477879</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28193</t>
+          <t>28407</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27014</t>
+          <t>26599</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>30023</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51604</t>
+          <t>49224</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19231</t>
+          <t>21262</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30576</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>444210</t>
+          <t>444089</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>500175</t>
+          <t>498768</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>620171</t>
+          <t>620036</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>756770</t>
+          <t>764390</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1095642</t>
+          <t>1096211</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1258678</t>
+          <t>1277658</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>87,39%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>83559</t>
+          <t>85823</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>135423</t>
+          <t>138138</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>61439</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>173302</t>
+          <t>173822</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>152563</t>
+          <t>143784</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>282368</t>
+          <t>279750</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>23920</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52320</t>
+          <t>52158</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19535</t>
+          <t>16739</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57127</t>
+          <t>57178</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>46975</t>
+          <t>48102</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>96010</t>
+          <t>97973</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>756123</t>
+          <t>753623</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>877167</t>
+          <t>871551</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>538946</t>
+          <t>539936</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>577279</t>
+          <t>576125</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1306901</t>
+          <t>1303794</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1469912</t>
+          <t>1469056</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>37457</t>
+          <t>39658</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>117674</t>
+          <t>120218</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>87983</t>
+          <t>88859</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>120485</t>
+          <t>119008</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>114826</t>
+          <t>112113</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>223609</t>
+          <t>225360</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>61293</t>
+          <t>61670</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>44167</t>
+          <t>42227</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>69964</t>
+          <t>69088</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>57861</t>
+          <t>60621</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>120957</t>
+          <t>121881</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2841358</t>
+          <t>2847254</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3029487</t>
+          <t>3023150</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3030929</t>
+          <t>3030764</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3196334</t>
+          <t>3201188</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5901152</t>
+          <t>5907290</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6136752</t>
+          <t>6173974</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>309567</t>
+          <t>310272</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>447893</t>
+          <t>448554</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>383699</t>
+          <t>379159</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>514116</t>
+          <t>511904</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>761411</t>
+          <t>740484</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>946380</t>
+          <t>941858</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>109900</t>
+          <t>111463</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>181725</t>
+          <t>179065</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>117127</t>
+          <t>117452</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>171050</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>249303</t>
+          <t>239972</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>334324</t>
+          <t>330670</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P05A06-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142877</t>
+          <t>142583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177786</t>
+          <t>177068</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>120530</t>
+          <t>118643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155611</t>
+          <t>154523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>272283</t>
+          <t>274523</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321935</t>
+          <t>322272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84204</t>
+          <t>80677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116628</t>
+          <t>113811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93035</t>
+          <t>92183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125910</t>
+          <t>128094</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184933</t>
+          <t>184858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232662</t>
+          <t>232190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40368</t>
+          <t>41705</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43321</t>
+          <t>42574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46575</t>
+          <t>45922</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76101</t>
+          <t>75664</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316546</t>
+          <t>315760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360791</t>
+          <t>359418</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325350</t>
+          <t>328385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369755</t>
+          <t>372158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>656628</t>
+          <t>653112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718576</t>
+          <t>715169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130863</t>
+          <t>130370</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174225</t>
+          <t>171992</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131057</t>
+          <t>128774</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>173954</t>
+          <t>171696</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>270798</t>
+          <t>274787</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>331404</t>
+          <t>334305</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>24068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31377</t>
+          <t>31911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24339</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49951</t>
+          <t>50627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>261363</t>
+          <t>262192</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>286184</t>
+          <t>286232</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>281994</t>
+          <t>280580</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>307551</t>
+          <t>306402</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>550854</t>
+          <t>551964</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>587305</t>
+          <t>590071</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35429</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59405</t>
+          <t>58933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30476</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55640</t>
+          <t>56065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72145</t>
+          <t>68839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107479</t>
+          <t>106003</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>227139</t>
+          <t>227197</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>266208</t>
+          <t>268141</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>237354</t>
+          <t>234918</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>272946</t>
+          <t>275000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>476934</t>
+          <t>476248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>532098</t>
+          <t>528408</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>69,93%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82922</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118920</t>
+          <t>118821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96727</t>
+          <t>96401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131585</t>
+          <t>135019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187218</t>
+          <t>188991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241118</t>
+          <t>239621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>34422</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>26179</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28319</t>
+          <t>28333</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52536</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>114431</t>
+          <t>113228</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>142930</t>
+          <t>144001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>107171</t>
+          <t>107229</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>138372</t>
+          <t>137092</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>231579</t>
+          <t>229463</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273523</t>
+          <t>273519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>48436</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75283</t>
+          <t>75822</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68647</t>
+          <t>69686</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98203</t>
+          <t>98103</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>124810</t>
+          <t>125259</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>164827</t>
+          <t>165753</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>34323</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22753</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>205816</t>
+          <t>206461</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>233036</t>
+          <t>232438</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>198009</t>
+          <t>198465</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>226893</t>
+          <t>225765</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>415917</t>
+          <t>413580</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>453166</t>
+          <t>451991</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60939</t>
+          <t>60782</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48915</t>
+          <t>48337</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77369</t>
+          <t>76271</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91967</t>
+          <t>91563</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>128435</t>
+          <t>129566</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>472028</t>
+          <t>475820</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>518033</t>
+          <t>518439</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>515182</t>
+          <t>515497</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>561394</t>
+          <t>561730</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1002771</t>
+          <t>999844</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1066788</t>
+          <t>1067728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>125785</t>
+          <t>126763</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>170661</t>
+          <t>167592</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>116325</t>
+          <t>115655</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>161149</t>
+          <t>160877</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>253263</t>
+          <t>253363</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>316017</t>
+          <t>318873</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>22989</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>25300</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19584</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42150</t>
+          <t>40803</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>530646</t>
+          <t>531559</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>581492</t>
+          <t>583481</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>571267</t>
+          <t>572856</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>624442</t>
+          <t>626443</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1115754</t>
+          <t>1117311</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1189938</t>
+          <t>1192945</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,52%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>173080</t>
+          <t>172461</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>223001</t>
+          <t>222839</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>182027</t>
+          <t>183793</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>235554</t>
+          <t>233987</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>369628</t>
+          <t>369361</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>443101</t>
+          <t>441492</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>34970</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27630</t>
+          <t>27044</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29551</t>
+          <t>27875</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55718</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2373160</t>
+          <t>2370101</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2480058</t>
+          <t>2476910</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2451318</t>
+          <t>2446841</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2558730</t>
+          <t>2562951</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4862065</t>
+          <t>4861156</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5015343</t>
+          <t>5014272</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>796370</t>
+          <t>800218</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>895318</t>
+          <t>903311</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>863626</t>
+          <t>858300</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>967037</t>
+          <t>967731</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1683984</t>
+          <t>1685004</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1830193</t>
+          <t>1831957</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>113910</t>
+          <t>110594</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>159441</t>
+          <t>159516</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>97803</t>
+          <t>96256</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>141059</t>
+          <t>139641</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>221422</t>
+          <t>219098</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>285568</t>
+          <t>286805</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145807</t>
+          <t>148239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182097</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139373</t>
+          <t>139836</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173631</t>
+          <t>174568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>297128</t>
+          <t>298607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>346397</t>
+          <t>347219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86979</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121675</t>
+          <t>120183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88547</t>
+          <t>87908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121992</t>
+          <t>121205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184981</t>
+          <t>185852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233373</t>
+          <t>230481</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29667</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>31940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54130</t>
+          <t>55460</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>326061</t>
+          <t>324661</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367701</t>
+          <t>366156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353851</t>
+          <t>356417</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>396074</t>
+          <t>397470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692881</t>
+          <t>695867</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>751420</t>
+          <t>755471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114242</t>
+          <t>113130</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153125</t>
+          <t>153387</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105283</t>
+          <t>102656</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143404</t>
+          <t>143962</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>228911</t>
+          <t>226937</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>285753</t>
+          <t>285110</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31907</t>
+          <t>33354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>31215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57954</t>
+          <t>57843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>240311</t>
+          <t>239202</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>267157</t>
+          <t>266825</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>255334</t>
+          <t>256598</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>284387</t>
+          <t>283810</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>505543</t>
+          <t>505332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>544818</t>
+          <t>544591</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>45885</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72230</t>
+          <t>73290</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47399</t>
+          <t>47553</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76179</t>
+          <t>74922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100005</t>
+          <t>101505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138850</t>
+          <t>140214</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17655</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>252551</t>
+          <t>249684</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>286188</t>
+          <t>284466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>266546</t>
+          <t>264987</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>300390</t>
+          <t>301373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>530901</t>
+          <t>527178</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>578268</t>
+          <t>575383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59384</t>
+          <t>60201</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89769</t>
+          <t>91656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58194</t>
+          <t>57291</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87601</t>
+          <t>87290</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126002</t>
+          <t>124622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>168943</t>
+          <t>168273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>14936</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34179</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35856</t>
+          <t>35955</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63099</t>
+          <t>63461</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>173190</t>
+          <t>172862</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192442</t>
+          <t>192572</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>176364</t>
+          <t>175567</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>196616</t>
+          <t>196681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356844</t>
+          <t>356738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384040</t>
+          <t>383539</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32549</t>
+          <t>33116</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31624</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>54621</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25412</t>
+          <t>25335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>224675</t>
+          <t>225060</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245135</t>
+          <t>245466</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>238718</t>
+          <t>239575</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>257725</t>
+          <t>258004</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>470417</t>
+          <t>471189</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>498254</t>
+          <t>498949</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33588</t>
+          <t>34324</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14076</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>32505</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>32998</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59207</t>
+          <t>59623</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>401242</t>
+          <t>401878</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>450728</t>
+          <t>452380</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>409929</t>
+          <t>411478</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>461162</t>
+          <t>462685</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,47 +7858,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>67,57%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>863893</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>825084</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>900018</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>64,64%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>61,74%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>67,35%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>863893</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>828543</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>897139</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>64,64%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>62,0%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>177668</t>
+          <t>175748</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>226182</t>
+          <t>224493</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>200618</t>
+          <t>197068</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>251558</t>
+          <t>248625</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>392194</t>
+          <t>387328</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>459555</t>
+          <t>463607</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34240</t>
+          <t>34039</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,49 +8049,49 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>23513</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>14686</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>35917</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
           <t>5,25%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>23513</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>15706</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>35873</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>43</t>
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34065</t>
+          <t>34886</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61313</t>
+          <t>64253</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>674304</t>
+          <t>675812</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>708619</t>
+          <t>709488</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,47 +8279,47 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>91,37%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>712031</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>690132</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>731893</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
           <t>86,84%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>91,26%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>712031</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>691167</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>732116</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>86,84%</t>
-        </is>
-      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1377243</t>
+          <t>1375556</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1431797</t>
+          <t>1430611</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>54583</t>
+          <t>53552</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>85782</t>
+          <t>85342</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>73853</t>
+          <t>74286</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>113288</t>
+          <t>112851</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>136368</t>
+          <t>137330</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>188341</t>
+          <t>185230</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>23713</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25681</t>
+          <t>24215</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21149</t>
+          <t>21673</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>41990</t>
+          <t>42458</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2530597</t>
+          <t>2524371</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2631855</t>
+          <t>2622349</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2625532</t>
+          <t>2624186</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2731399</t>
+          <t>2726526</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5180660</t>
+          <t>5177574</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5323665</t>
+          <t>5315483</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>634101</t>
+          <t>636677</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>727126</t>
+          <t>729294</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>667810</t>
+          <t>669863</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>768259</t>
+          <t>766943</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1329451</t>
+          <t>1340613</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1472085</t>
+          <t>1476494</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>98658</t>
+          <t>98144</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>141005</t>
+          <t>139187</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>98995</t>
+          <t>100001</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>141886</t>
+          <t>143598</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>207527</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>270301</t>
+          <t>269485</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -9407,32 +9407,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>299152</t>
+          <t>298783</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>291105</t>
+          <t>289292</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>304236</t>
+          <t>305569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9442,32 +9442,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>272639</t>
+          <t>297690</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>253358</t>
+          <t>286969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279389</t>
+          <t>304027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9477,32 +9477,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>571791</t>
+          <t>596473</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>552065</t>
+          <t>583753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>580766</t>
+          <t>607038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -9520,32 +9520,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9555,67 +9555,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36080</t>
+          <t>28978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>36857</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>26637</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>49877</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>27839</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>18893</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>47718</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>498</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -9678,12 +9678,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>498</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -9713,12 +9713,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -9746,17 +9746,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9816,17 +9816,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>397141</t>
+          <t>405362</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368414</t>
+          <t>379831</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420591</t>
+          <t>426954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9898,32 +9898,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>394749</t>
+          <t>416173</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>374825</t>
+          <t>397203</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>411818</t>
+          <t>434231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9933,32 +9933,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>791890</t>
+          <t>821534</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>758763</t>
+          <t>787843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>818694</t>
+          <t>852115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -9976,32 +9976,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92104</t>
+          <t>96755</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70394</t>
+          <t>76533</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>115895</t>
+          <t>120554</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10011,32 +10011,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>104827</t>
+          <t>113422</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87899</t>
+          <t>95794</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124412</t>
+          <t>132830</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10046,32 +10046,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>196931</t>
+          <t>210178</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>168810</t>
+          <t>181416</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>227132</t>
+          <t>240484</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -10089,32 +10089,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51014</t>
+          <t>45523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20829</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10159,32 +10159,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>42630</t>
+          <t>43512</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64709</t>
+          <t>65629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -10202,17 +10202,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10237,17 +10237,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>513062</t>
+          <t>544577</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>513062</t>
+          <t>544577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>513062</t>
+          <t>544577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10272,17 +10272,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1031452</t>
+          <t>1075224</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1031452</t>
+          <t>1075224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031452</t>
+          <t>1075224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10319,32 +10319,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>268607</t>
+          <t>266892</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>255338</t>
+          <t>251388</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>281232</t>
+          <t>277860</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10354,27 +10354,27 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>300403</t>
+          <t>306555</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>287408</t>
+          <t>294682</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>311032</t>
+          <t>317489</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -10389,32 +10389,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>569009</t>
+          <t>573447</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>549645</t>
+          <t>555144</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>585656</t>
+          <t>589397</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -10432,32 +10432,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27071</t>
+          <t>29146</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18543</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38010</t>
+          <t>41210</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10467,32 +10467,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31796</t>
+          <t>32272</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22781</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>43511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10502,32 +10502,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>58867</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46862</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73983</t>
+          <t>75727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -10545,32 +10545,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30306</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10580,32 +10580,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>17554</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>26556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10615,32 +10615,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>36281</t>
+          <t>36425</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26251</t>
+          <t>26840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50460</t>
+          <t>48666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -10658,17 +10658,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>315031</t>
+          <t>314908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>315031</t>
+          <t>314908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>315031</t>
+          <t>314908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10693,17 +10693,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10728,17 +10728,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>664158</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>664158</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>664158</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10775,32 +10775,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>260625</t>
+          <t>314960</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>243342</t>
+          <t>295693</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>274050</t>
+          <t>330974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10810,34 +10810,34 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>415969</t>
+          <t>355789</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>396565</t>
+          <t>338974</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>439326</t>
+          <t>368778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>84,55%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>80,55%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>87,63%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>83,55%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>92,55%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>737</t>
@@ -10845,32 +10845,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>676593</t>
+          <t>670749</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>651596</t>
+          <t>645669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>706987</t>
+          <t>691501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -10888,32 +10888,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42722</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58047</t>
+          <t>65467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10923,32 +10923,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46461</t>
+          <t>51954</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>40656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62774</t>
+          <t>66938</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10958,32 +10958,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>89182</t>
+          <t>100337</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63205</t>
+          <t>83091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111610</t>
+          <t>123461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -11001,32 +11001,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21321</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11036,32 +11036,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23589</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11071,32 +11071,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36096</t>
+          <t>39759</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -11114,17 +11114,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>311973</t>
+          <t>372557</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>311973</t>
+          <t>372557</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>311973</t>
+          <t>372557</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11149,17 +11149,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>474669</t>
+          <t>420824</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>474669</t>
+          <t>420824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>474669</t>
+          <t>420824</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11184,17 +11184,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>786642</t>
+          <t>793381</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>786642</t>
+          <t>793381</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>786642</t>
+          <t>793381</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11231,32 +11231,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>163785</t>
+          <t>188521</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153880</t>
+          <t>179213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169100</t>
+          <t>194601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11266,32 +11266,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>244492</t>
+          <t>213691</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237919</t>
+          <t>207648</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251369</t>
+          <t>217972</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11301,32 +11301,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>408277</t>
+          <t>402211</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>397847</t>
+          <t>391555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>418323</t>
+          <t>411107</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -11344,32 +11344,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>25663</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11379,32 +11379,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>15227</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11414,32 +11414,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>31365</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39336</t>
+          <t>43157</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -11570,17 +11570,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11640,17 +11640,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11687,32 +11687,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>236907</t>
+          <t>237546</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>225457</t>
+          <t>226942</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245580</t>
+          <t>246341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11722,32 +11722,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>228618</t>
+          <t>234219</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>220476</t>
+          <t>224644</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>236364</t>
+          <t>241663</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11757,32 +11757,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>465524</t>
+          <t>471766</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>453148</t>
+          <t>456158</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>477879</t>
+          <t>482483</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -11800,32 +11800,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>14498</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28407</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11835,32 +11835,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19178</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11870,32 +11870,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>39705</t>
+          <t>41628</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30023</t>
+          <t>32714</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49224</t>
+          <t>52882</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -11913,32 +11913,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11948,17 +11948,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11983,32 +11983,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>21062</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>31144</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -12026,17 +12026,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269236</t>
+          <t>270283</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269236</t>
+          <t>270283</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269236</t>
+          <t>270283</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12061,17 +12061,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12096,17 +12096,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526291</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526291</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526291</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12143,32 +12143,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>475123</t>
+          <t>560592</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>444089</t>
+          <t>534941</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>498768</t>
+          <t>587644</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12178,32 +12178,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>681628</t>
+          <t>574436</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>620036</t>
+          <t>548435</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>764390</t>
+          <t>596908</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12213,32 +12213,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1156751</t>
+          <t>1135028</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1096211</t>
+          <t>1097354</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1277658</t>
+          <t>1163963</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -12256,32 +12256,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>106619</t>
+          <t>110858</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>85823</t>
+          <t>88486</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138138</t>
+          <t>133986</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12291,32 +12291,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>125253</t>
+          <t>147484</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>61439</t>
+          <t>128229</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>173822</t>
+          <t>171624</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12326,32 +12326,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>231872</t>
+          <t>258342</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>143784</t>
+          <t>230486</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>279750</t>
+          <t>292405</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -12369,32 +12369,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>35448</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>26757</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52158</t>
+          <t>56410</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12404,32 +12404,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>38021</t>
+          <t>43844</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>33031</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57178</t>
+          <t>59226</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12439,32 +12439,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>73470</t>
+          <t>82449</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48102</t>
+          <t>65929</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>97973</t>
+          <t>105685</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -12482,17 +12482,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>617190</t>
+          <t>710054</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>617190</t>
+          <t>710054</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>617190</t>
+          <t>710054</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12517,17 +12517,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>844903</t>
+          <t>765765</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>844903</t>
+          <t>765765</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>844903</t>
+          <t>765765</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12552,17 +12552,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1462093</t>
+          <t>1475819</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1462093</t>
+          <t>1475819</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1462093</t>
+          <t>1475819</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12599,32 +12599,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>806817</t>
+          <t>653697</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>753623</t>
+          <t>628369</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>871551</t>
+          <t>675859</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12634,32 +12634,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>557191</t>
+          <t>637938</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>539936</t>
+          <t>613222</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>576125</t>
+          <t>659286</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12669,32 +12669,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1364008</t>
+          <t>1291635</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1303794</t>
+          <t>1259766</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1469056</t>
+          <t>1324247</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -12712,32 +12712,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>81425</t>
+          <t>93320</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>39658</t>
+          <t>75734</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>120218</t>
+          <t>113645</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12747,32 +12747,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>103014</t>
+          <t>119042</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>88859</t>
+          <t>102440</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>119008</t>
+          <t>138836</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12782,32 +12782,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>184440</t>
+          <t>212363</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>112113</t>
+          <t>186469</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>225360</t>
+          <t>238715</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -12825,32 +12825,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>40478</t>
+          <t>51054</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>37852</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>61670</t>
+          <t>67806</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12860,32 +12860,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>55207</t>
+          <t>71751</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>42227</t>
+          <t>58503</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>69088</t>
+          <t>89494</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12895,32 +12895,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>95685</t>
+          <t>122805</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>60621</t>
+          <t>102998</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>121881</t>
+          <t>145710</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -12938,17 +12938,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12973,17 +12973,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>715412</t>
+          <t>828731</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>715412</t>
+          <t>828731</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>715412</t>
+          <t>828731</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13008,17 +13008,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1644132</t>
+          <t>1626803</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1644132</t>
+          <t>1626803</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1644132</t>
+          <t>1626803</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13055,32 +13055,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2908157</t>
+          <t>2926353</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2847254</t>
+          <t>2870584</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3023150</t>
+          <t>2974759</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13090,32 +13090,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3095688</t>
+          <t>3036490</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3030764</t>
+          <t>2985912</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3201188</t>
+          <t>3078779</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13125,32 +13125,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>6003845</t>
+          <t>5962844</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5907290</t>
+          <t>5897423</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6173974</t>
+          <t>6029137</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -13168,32 +13168,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>396272</t>
+          <t>435167</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>310272</t>
+          <t>394162</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>482171</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13203,32 +13203,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>461647</t>
+          <t>517320</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>379159</t>
+          <t>480748</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>511904</t>
+          <t>564479</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13238,32 +13238,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>857919</t>
+          <t>952487</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>740484</t>
+          <t>892278</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>941858</t>
+          <t>1012514</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -13281,32 +13281,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>145015</t>
+          <t>158433</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>111463</t>
+          <t>133446</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>179065</t>
+          <t>193593</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13316,32 +13316,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>145308</t>
+          <t>171197</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>117452</t>
+          <t>146893</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>171050</t>
+          <t>198268</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13351,32 +13351,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>290323</t>
+          <t>329630</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>239972</t>
+          <t>293762</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>330670</t>
+          <t>370437</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -13394,17 +13394,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3449443</t>
+          <t>3519953</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3449443</t>
+          <t>3519953</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3449443</t>
+          <t>3519953</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13429,17 +13429,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3702643</t>
+          <t>3725007</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3702643</t>
+          <t>3725007</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3702643</t>
+          <t>3725007</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13464,17 +13464,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7152086</t>
+          <t>7244961</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7152086</t>
+          <t>7244961</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7152086</t>
+          <t>7244961</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
